--- a/Applied-Research Project/05-Implementation/02_Atomic_Red_Teams_Attack_Scenarios/02_T1087.001_Local_Account_Discovery/02_Ground_Truth/Scenario_2.xlsx
+++ b/Applied-Research Project/05-Implementation/02_Atomic_Red_Teams_Attack_Scenarios/02_T1087.001_Local_Account_Discovery/02_Ground_Truth/Scenario_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\darra\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\darra\Documents\GitHub\applied-research-project\Applied-Research Project\05-Implementation\02_Atomic_Red_Teams_Attack_Scenarios\02_T1087.001_Local_Account_Discovery\02_Ground_Truth\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89146C5E-EE63-494C-9091-818ADD9A634A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C19732-8878-49E8-9267-C44D2282CF31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6EDD1CA0-2A49-4EF7-89EA-F85052302D67}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{6EDD1CA0-2A49-4EF7-89EA-F85052302D67}"/>
   </bookViews>
   <sheets>
     <sheet name="Scenario 1" sheetId="1" r:id="rId1"/>
@@ -86,32 +86,18 @@
     <t>Execution &amp; timing</t>
   </si>
   <si>
-    <t>Sysmon Event ID 1
-EventRecordID 15251
-Wazuh Rule 92004.</t>
-  </si>
-  <si>
     <t>GT2</t>
   </si>
   <si>
     <t>GT3</t>
   </si>
   <si>
-    <t>Sysmon Event ID 1
-EventRecordID 15251
-ProcessGuid {4b2ce92d-c5df-6abf-8104-000000001400}.</t>
-  </si>
-  <si>
     <t>GT4</t>
   </si>
   <si>
     <t>GT5</t>
   </si>
   <si>
-    <t>Sysmon Event ID 1
-EventRecordID 15251.</t>
-  </si>
-  <si>
     <t>GT6</t>
   </si>
   <si>
@@ -130,103 +116,114 @@
     <t>ATT&amp;CK &amp; sequence</t>
   </si>
   <si>
-    <t>EventRecordIDs 15248, 15251
-Wazuh Rule 92004.</t>
-  </si>
-  <si>
-    <t>EventRecordID 15248, 15251</t>
-  </si>
-  <si>
-    <t>Enumerate all accounts on Windows (Local)</t>
-  </si>
-  <si>
     <t>T1087.001</t>
   </si>
   <si>
-    <t>Account Discovery: Local Account</t>
-  </si>
-  <si>
-    <t>2026-10-03 16:26:15.192 UTC / 18:26:15.192 (UTC+2)</t>
-  </si>
-  <si>
-    <t>2026-10-03: 18:21:20.122 - 18:31:03.472 (UTC+2)</t>
+    <t>Local Account Discovery</t>
+  </si>
+  <si>
+    <t>2026-10-27 11:34:42.460 UTC / 12:34:42.460 (UTC+1)</t>
+  </si>
+  <si>
+    <t>2026-10-27: 12:29:43.130–12:34:49.427 (UTC+1)</t>
+  </si>
+  <si>
+    <t>Scenario_2_Archives.json / Scenario_2_Alerts.json</t>
+  </si>
+  <si>
+    <t>Enumerate all accounts (Local)</t>
   </si>
   <si>
     <t>• Host: DESKTOP-5OG7C28
 • Atomic test: Enumerate all accounts on Windows (Local)
-• Main process: cmd.exe, PID 11280
-• Execution: 2026-10-03 16:26:15.192 UTC / 18:26:15.192 (UTC+2)</t>
-  </si>
-  <si>
-    <t>• Record 15599 contains the full command line
-• 15600–15601: net user / net1 user
-• 15602: cmdkey.exe /list
-• 15603–15606: net / net1 localgroup variants
-• dir is a cmd built-in; no separate process expected
-• Command stdout and directory listing are not supplied.</t>
-  </si>
-  <si>
-    <t>• Parent: powershell.exe, PID 5664
-• Child: cmd.exe, PID 11280
+• Main process: cmd.exe, PID 1832 (executes local account discovery commands)
+• Execution: 11:34:42.460 UTC / 12:34:42.460 (UTC+1)</t>
+  </si>
+  <si>
+    <t>• Sysmon Process Create records cmd.exe with PowerShell parent PID 12276. Timestamp: 2026-10-27 11:34:42:460
+• Wazuh Rule 92052 alert timestamp: 12:34:48.637+0100
+• hostname.exe and whoami.exe launches immediately precede cmd.exe</t>
+  </si>
+  <si>
+    <t>Sysmon Event ID 1; EventRecordIDs 28312–28318
+Wazuh Rule 92052 (RecordID 28318)</t>
+  </si>
+  <si>
+    <t>• cmd.exe /c launched: net user; dir C:\Users\; cmdkey.exe /list; net localgroup "Users"; net localgroup
+• Intended checks: accounts, user folders, stored credentials and local groups
+• 'dir' appears in the shell command line; its output is not supplied</t>
+  </si>
+  <si>
+    <t>• Record 28318 contains the full chained command line
+• Records 28319–28320: net / net1 user
+• Record 28321: cmdkey.exe /list
+• Records 28322–28325: net / net1 localgroup commands</t>
+  </si>
+  <si>
+    <t>Sysmon Event ID 1; EventRecordIDs 28318–28325
+Wazuh Rules 92052, 92036, 92031, 92032</t>
+  </si>
+  <si>
+    <t>• Parent: powershell.exe, PID 12276
+• Child: cmd.exe, PID 1832
 • User: DESKTOP-5OG7C28\Darragh Casey
-• Integrity: High; TerminalSessionId: 1
-• LogonId: 0xA8D6D
-• Child utilities: net.exe, net1.exe, cmdkey.exe</t>
-  </si>
-  <si>
-    <t>• Record 15599 identifies PowerShell as parent, with user, integrity and session details
-• Records 15600–15606 establish the process parent–child relationships for net.exe, net1.exe and cmdkey.exe.</t>
-  </si>
-  <si>
-    <t>• 15600–15601: net user and net1 user
-• 15602 + Security 54371: cmdkey.exe /list; client PID 11524
-• 15603–15604 + Security 54372: Users membership enumeration; caller PID 1768 (net1.exe)
-• 15605–15606: general localgroup listing processes.</t>
-  </si>
-  <si>
-    <t>• Wazuh 92052 (level 4): cmd.exe with unusual parent
-• Wazuh 92036 (level 3): net.exe from cmd shell (3 alerts)
-• Wazuh 92031 (level 3): net1.exe discovery (3 alerts)
-• Wazuh 92032 (level 3): cmdkey.exe (1 alert)
-• Rules 92031/92032 tag parent technique T1087; no alert explicitly tags T1087.001.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• cmd.exe /c ran the chained command:
-  net user &amp; dir c:\Users\ &amp; cmdkey.exe /list &amp; net localgroup "Users" &amp; net localgroup
-</t>
-  </si>
-  <si>
-    <t>• Execution of local-account and local-group discovery commands is confirmed
-• Security event 4799 shows that the Built-in Users group membership was listed.
-• Security 5379 records a credential read by cmdkey.exe (one credential returned; return code 0)
-• Actual account listings, credential values and stdout are not in the provided logs.</t>
-  </si>
-  <si>
-    <t>• Sysmon Process Create: cmd.exe at 16:26:15.205Z (system timestamp)
-• Corresponding Wazuh alert at 18:26:14.563+0200
-•The Wazuh alert time is a little earlier than the Sysmon event time. Do not treat the exact timing between the two as precise.</t>
-  </si>
-  <si>
-    <t>• MITRE ATT&amp;CK: T1087.001 – Account Discovery: Local Account
-• Tactic: Discovery
-• Test GUID: 80887bec-5a9b-4efc-a81d-f83eb2eb32ab
-• Observed sequence:
-PowerShell (5664) 
-cmd.exe (11280) 
-net.exe / net1.exe 
-cmdkey.exe</t>
-  </si>
-  <si>
-    <t>• Sysmon 15599–15606 traces the command and child processes
-• Security 54371 and 54372 confirms credential read and group-member enumeration</t>
-  </si>
-  <si>
-    <t>• Wazuh process alerts match Sysmon 15599–15606
-• Rule 92052 tags command-shell T1059.003
-• 92031/92032 include T1087 (Account Discovery)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scenario_2_Archives.json / Scenario_2_Alerts.json </t>
+• Integrity: High; session: 1; LogonId: 0xFCD15
+• Further children include net.exe, net1.exe and cmdkey.exe</t>
+  </si>
+  <si>
+    <t>• ParentProcessGuid on cmd.exe matches PowerShell lineage
+• cmd.exe launches net.exe PIDs 12068, 8816, 6504 and cmdkey.exe PID 7940
+• net.exe launches net1.exe PIDs 6584, 10484, 4912
+• Child telemetry carries the same user/logon info</t>
+  </si>
+  <si>
+    <t>Sysmon Event ID 1
+EventRecordIDs 28318–28325
+ProcessGUID: 4b2ce92d-8c52-6ae0-8c06-000000001a00</t>
+  </si>
+  <si>
+    <t>• Rule 92052 flags the unusual cmd.exe parent
+• Rule 92036 flags net.exe launched from cmd.exe
+• Rules 92031 / 92032 flag discovery and cmdkey activity
+• Security logs independently corroborate credential and group enumeration</t>
+  </si>
+  <si>
+    <t>Wazuh Rules 92052, 92036, 92031, 92032
+Sysmon RecordIDs 28318–28325
+Security RecordIDs 83505–83506</t>
+  </si>
+  <si>
+    <t>• Process launches confirm the discovery commands were invoked
+• Security Event 5379 records credential enumeration: 1 credential returned; return code 0
+• Security Event 4799 confirms BUILTIN\Users group membership was enumerated
+• Credential contents and command sdtout unavailable</t>
+  </si>
+  <si>
+    <t>• Event 5379 identifies client PID 7940 (cmdkey.exe)
+• Event 4799 identifies net1.exe, caller PID 0x28F4 (10484)
+• Both security events follow the relevant process creations in the archived logs</t>
+  </si>
+  <si>
+    <t>Windows Security Event IDs 5379 (RecordID 83505),
+4799 (RecordID 83506)
+Sysmon RecordIDs 28321, 28323</t>
+  </si>
+  <si>
+    <t>• T1087.001 (Local Account Discovery) is supported by alert labels and process logs
+• Some Rule 92036 alerts also list T1574.001
+• Test_2.ps1 was opened in Notepad; its execution is not proven while in the Powershell session
+• Does not confirm successful exfiltration or the contents of enumerated data</t>
+  </si>
+  <si>
+    <t>• 11:29:36.280 UTC: Notepad opens Test_2.ps1
+• 11:34:41.714–42.165 UTC: PowerShell launches hostname.exe / whoami.exe
+• 11:34:42.460–42.641 UTC: cmd.exe → net/net1/cmdkey processes
+• 11:34:42.570 / 42.612 UTC: Security 5379 / 4799 events</t>
+  </si>
+  <si>
+    <t>Sysmon RecordIDs 28307, 28312–28325
+Security RecordIDs 83505–83506
+Wazuh Rules 92052, 92031, 92032, 92036</t>
   </si>
 </sst>
 </file>
@@ -297,7 +294,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -337,6 +334,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -698,7 +698,7 @@
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="8"/>
@@ -710,7 +710,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="7"/>
@@ -721,7 +721,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="7"/>
@@ -732,7 +732,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="7"/>
@@ -743,7 +743,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="7"/>
@@ -754,7 +754,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="7"/>
@@ -777,7 +777,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:5" s="5" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" s="5" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>13</v>
       </c>
@@ -785,38 +785,38 @@
         <v>14</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>15</v>
+        <v>32</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:5" s="5" customFormat="1" ht="145.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" s="5" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>36</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" s="5" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="10" t="s">
-        <v>17</v>
-      </c>
       <c r="B11" s="11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>37</v>
@@ -824,59 +824,59 @@
       <c r="D11" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="E11" s="11" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" s="5" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="E11" s="16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" s="5" customFormat="1" ht="129.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>42</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" s="5" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" s="5" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A13" s="10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>40</v>
       </c>
       <c r="D13" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="16" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" s="5" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A14" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="11" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" s="5" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A14" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>45</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>28</v>
+      <c r="E14" s="16" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:5" s="5" customFormat="1" x14ac:dyDescent="0.3">
